--- a/VerveStacks_POL_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_POL_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AF6FAB2-0A92-46A3-9092-A5B8AA04AFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B02272D8-0ECE-4297-87CF-F8C1174BA0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="231">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -364,31 +364,61 @@
     <t>t_pos_andor</t>
   </si>
   <si>
-    <t>p_w139452056-400_POL</t>
-  </si>
-  <si>
-    <t>e_w139452056-400_POL*</t>
+    <t>p_w29115701-220_POL</t>
+  </si>
+  <si>
+    <t>e_w29115701-220_POL*</t>
   </si>
   <si>
     <t>OR</t>
   </si>
   <si>
-    <t>p_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>e_w183945016-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>e_w255277953-400_POL*</t>
-  </si>
-  <si>
-    <t>p_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>e_w44389929-220_POL*</t>
+    <t>p_w39428977-400_POL</t>
+  </si>
+  <si>
+    <t>e_w39428977-400_POL*</t>
+  </si>
+  <si>
+    <t>p_w86494356-400_POL</t>
+  </si>
+  <si>
+    <t>e_w86494356-400_POL*</t>
+  </si>
+  <si>
+    <t>p_w111615226-220_POL</t>
+  </si>
+  <si>
+    <t>e_w111615226-220_POL*</t>
+  </si>
+  <si>
+    <t>p_w133537926-220_POL</t>
+  </si>
+  <si>
+    <t>e_w133537926-220_POL*</t>
+  </si>
+  <si>
+    <t>p_w191035265-220_POL</t>
+  </si>
+  <si>
+    <t>e_w191035265-220_POL*</t>
+  </si>
+  <si>
+    <t>p_w293484891-220_POL</t>
+  </si>
+  <si>
+    <t>e_w293484891-220_POL*</t>
+  </si>
+  <si>
+    <t>p_PL75-220_POL</t>
+  </si>
+  <si>
+    <t>e_PL75-220_POL*</t>
+  </si>
+  <si>
+    <t>p_PL17-400_POL</t>
+  </si>
+  <si>
+    <t>e_PL17-400_POL*</t>
   </si>
   <si>
     <t>p_w303870256-400_POL</t>
@@ -397,82 +427,10 @@
     <t>e_w303870256-400_POL*</t>
   </si>
   <si>
-    <t>p_w29115701-220_POL</t>
-  </si>
-  <si>
-    <t>e_w29115701-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL*</t>
-  </si>
-  <si>
-    <t>p_w86494356-400_POL</t>
-  </si>
-  <si>
-    <t>e_w86494356-400_POL*</t>
-  </si>
-  <si>
-    <t>p_w111615226-220_POL</t>
-  </si>
-  <si>
-    <t>e_w111615226-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w133537926-220_POL</t>
-  </si>
-  <si>
-    <t>e_w133537926-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w191035265-220_POL</t>
-  </si>
-  <si>
-    <t>e_w191035265-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w293484891-220_POL</t>
-  </si>
-  <si>
-    <t>e_w293484891-220_POL*</t>
-  </si>
-  <si>
-    <t>p_PL75-220_POL</t>
-  </si>
-  <si>
-    <t>e_PL75-220_POL*</t>
-  </si>
-  <si>
-    <t>p_PL17-400_POL</t>
-  </si>
-  <si>
-    <t>e_PL17-400_POL*</t>
-  </si>
-  <si>
     <t>p_w255314292_POL</t>
   </si>
   <si>
     <t>e_w255314292_POL*</t>
-  </si>
-  <si>
-    <t>p_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL*</t>
-  </si>
-  <si>
-    <t>p_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>e_w173613665-220_POL*</t>
-  </si>
-  <si>
-    <t>p_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>e_w215282393-400_POL*</t>
   </si>
   <si>
     <t>rez_spv_POL_001</t>
@@ -1617,8 +1575,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A89E4D-3E0E-4E25-93E8-4097519B1700}">
-  <dimension ref="B9:E78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87D54ED-A556-4EED-A82B-C9492D8D28F6}">
+  <dimension ref="B9:E71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -2491,104 +2449,6 @@
         <v>230</v>
       </c>
       <c r="E71" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B72" t="s">
-        <v>231</v>
-      </c>
-      <c r="C72" t="s">
-        <v>232</v>
-      </c>
-      <c r="D72" t="s">
-        <v>232</v>
-      </c>
-      <c r="E72" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B73" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" t="s">
-        <v>234</v>
-      </c>
-      <c r="D73" t="s">
-        <v>234</v>
-      </c>
-      <c r="E73" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B74" t="s">
-        <v>235</v>
-      </c>
-      <c r="C74" t="s">
-        <v>236</v>
-      </c>
-      <c r="D74" t="s">
-        <v>236</v>
-      </c>
-      <c r="E74" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B75" t="s">
-        <v>237</v>
-      </c>
-      <c r="C75" t="s">
-        <v>238</v>
-      </c>
-      <c r="D75" t="s">
-        <v>238</v>
-      </c>
-      <c r="E75" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B76" t="s">
-        <v>239</v>
-      </c>
-      <c r="C76" t="s">
-        <v>240</v>
-      </c>
-      <c r="D76" t="s">
-        <v>240</v>
-      </c>
-      <c r="E76" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B77" t="s">
-        <v>241</v>
-      </c>
-      <c r="C77" t="s">
-        <v>242</v>
-      </c>
-      <c r="D77" t="s">
-        <v>242</v>
-      </c>
-      <c r="E77" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B78" t="s">
-        <v>243</v>
-      </c>
-      <c r="C78" t="s">
-        <v>244</v>
-      </c>
-      <c r="D78" t="s">
-        <v>244</v>
-      </c>
-      <c r="E78" t="s">
         <v>110</v>
       </c>
     </row>
